--- a/ExcelToJSONConverter/excel/guideQuest.xlsx
+++ b/ExcelToJSONConverter/excel/guideQuest.xlsx
@@ -3,13 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C05D4E4-86B5-4CEE-A106-51AB79595397}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A1E5157-9B7E-414E-9A75-BAA18A66B155}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2055" yWindow="2715" windowWidth="16200" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
     <sheet name="GuideQuest" sheetId="3" r:id="rId2"/>
+    <sheet name="GuideQuest_Repeat" sheetId="5" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="65">
   <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -37,110 +38,214 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>#설명</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ClassType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>지휘관</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>용장</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>선봉장</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>추격자</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>궁장</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>책사</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RegionType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>위</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>촉</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>오</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>중립</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>촉</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>위</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>오</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>master</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>startHero</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LiuBei</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>isActive</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>CaoRen,XiahouDun,ZhangLiao,XiahouYuan,XunYu</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GuanYu, ZhangFei,ZhaoYun,HuangZhong,ZhugeLiang</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>HuangGai,SunCe,TaishiCi,HanDang,ZhouYu</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CaoCao</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SunQuan</t>
-  </si>
-  <si>
     <t>#key</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MOVE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>start_stage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>target_value</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>navigation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reward_item</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reward_count</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#reward</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rice</t>
+  </si>
+  <si>
+    <t>gold</t>
+  </si>
+  <si>
+    <t>time_stone</t>
+  </si>
+  <si>
+    <t>bundle_normal</t>
+  </si>
+  <si>
+    <t>bundle_elite</t>
+  </si>
+  <si>
+    <t>bundle_general</t>
+  </si>
+  <si>
+    <t>bundle_hero</t>
+  </si>
+  <si>
+    <t>bundle_legend</t>
+  </si>
+  <si>
+    <t>public_soul_stone</t>
+  </si>
+  <si>
+    <t>class_soul_stone</t>
+  </si>
+  <si>
+    <t>dedicated_soul_stone</t>
+  </si>
+  <si>
+    <t>class_soul_stone_random_box</t>
+  </si>
+  <si>
+    <t>dedicated_soul_stone_random_box</t>
+  </si>
+  <si>
+    <t>treasure</t>
+  </si>
+  <si>
+    <t>treasure_piece</t>
+  </si>
+  <si>
+    <t>treasure_piece_random_box</t>
+  </si>
+  <si>
+    <t>normal_gatcha_ticket</t>
+  </si>
+  <si>
+    <t>rare_gatcha_ticket</t>
+  </si>
+  <si>
+    <t>ENEMY_KILL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TOURNAMENT_PLAY</t>
+  </si>
+  <si>
+    <t>RAID_PLAY</t>
+  </si>
+  <si>
+    <t>GACHA_PROGRESS</t>
+  </si>
+  <si>
+    <t>FARM_RICE_EARN</t>
+  </si>
+  <si>
+    <t>MARKET_GOLD_EARN</t>
+  </si>
+  <si>
+    <t>OFFICE_MISSION_PROGRESS</t>
+  </si>
+  <si>
+    <t>DAILY_DUNGEON_PLAY</t>
+  </si>
+  <si>
+    <t>STAGE_BOSS_KILL</t>
+  </si>
+  <si>
+    <t>character</t>
+  </si>
+  <si>
+    <t>castle</t>
+  </si>
+  <si>
+    <t>dungeon</t>
+  </si>
+  <si>
+    <t>shop</t>
+  </si>
+  <si>
+    <t>gacha</t>
+  </si>
+  <si>
+    <t>story</t>
+  </si>
+  <si>
+    <t>raid</t>
+  </si>
+  <si>
+    <t>profile</t>
+  </si>
+  <si>
+    <t>tournament</t>
+  </si>
+  <si>
+    <t>#navigation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1-2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>castle,office,2</t>
+  </si>
+  <si>
+    <t>story</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>character</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>open_guide_key</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TOURNAMENT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RAID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GACHA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CASTLE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DAILY_DUNGEON</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NORMAL_ATTACK</t>
+  </si>
+  <si>
+    <t>MAIN_SKILL_USE</t>
+  </si>
+  <si>
+    <t>DASH_USE</t>
+  </si>
+  <si>
+    <t>STORYMODE_PLAY</t>
+  </si>
+  <si>
+    <t>CHARACTER_DEPLOY</t>
+  </si>
+  <si>
+    <t>gold</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -148,7 +253,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -173,6 +278,12 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -188,7 +299,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -211,38 +322,39 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -582,87 +694,234 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A2:E19"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="35.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="D2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3">
+        <f t="shared" ref="B3:B18" si="0">B2+1</f>
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E3">
+        <f t="shared" ref="E3:E9" si="1">E2+1</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="D4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E4">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E5">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="D6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="D7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="D8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="D9" t="s">
+        <v>45</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="D10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E10">
+        <f t="shared" ref="E10" si="2">E9+1</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12">
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2" t="s">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13">
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3" t="s">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14">
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4">
-        <v>2</v>
-      </c>
-      <c r="E4" t="s">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15">
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5" t="s">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16">
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
-        <v>9</v>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19">
+        <f>B18+1</f>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -674,125 +933,197 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.625" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.375" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="62.375" customWidth="1"/>
+    <col min="1" max="1" width="6.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.5" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="12.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" t="str">
-        <f>"GUIDE_"&amp;TEXT(A3,"0000")</f>
-        <v>GUIDE_0001</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <f>A3+1</f>
+      <c r="G2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" t="str">
-        <f>"GUIDE_"&amp;TEXT(A4,"0000")</f>
-        <v>GUIDE_0002</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <f>A4+1</f>
-        <v>3</v>
-      </c>
-      <c r="B5" t="str">
-        <f>"GUIDE_"&amp;TEXT(A5,"0000")</f>
-        <v>GUIDE_0003</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B6" s="3"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B7" s="3"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B8" s="3"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B9" s="3"/>
+      <c r="H2" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="7"/>
+      <c r="B3" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="3">
+        <f>VLOOKUP(F3,Overview!$A$2:$B$19,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="H3" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="7"/>
+      <c r="B4" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4" s="8"/>
+      <c r="D4" s="7">
+        <v>5</v>
+      </c>
+      <c r="E4" s="7"/>
+      <c r="F4" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="G4" s="3">
+        <f>VLOOKUP(F4,Overview!$A$2:$B$19,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="7"/>
+      <c r="B5" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C5" s="8"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="3">
+        <f>VLOOKUP(F5,Overview!$A$2:$B$19,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="H5" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="7"/>
+      <c r="B6" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="8"/>
+      <c r="D6" s="7">
+        <v>2</v>
+      </c>
+      <c r="E6" s="7"/>
+      <c r="F6" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="G6" s="3">
+        <f>VLOOKUP(F6,Overview!$A$2:$B$19,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H6" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="7"/>
+      <c r="B7" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" s="3">
+        <f>VLOOKUP(F7,Overview!$A$2:$B$19,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="H7" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="7"/>
+      <c r="B8" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C8" s="8"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="G8" s="3">
+        <f>VLOOKUP(F8,Overview!$A$2:$B$19,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H8" s="7">
+        <v>100</v>
+      </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:B41">
@@ -802,4 +1133,312 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75BF01C2-6BFB-4CCC-9124-BCB4513B4E3A}">
+  <dimension ref="A1:J11"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="6.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.75" style="2" customWidth="1"/>
+    <col min="6" max="6" width="14.375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="11.125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="12.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="29.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3">
+        <v>10</v>
+      </c>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" s="3">
+        <f>VLOOKUP(G3,Overview!$A$2:$B$19,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="I3" s="3">
+        <v>100</v>
+      </c>
+      <c r="J3" s="7"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="3">
+        <f>VLOOKUP(G4,Overview!$A$2:$B$19,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="I4" s="3">
+        <v>100</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" s="3">
+        <f>VLOOKUP(G5,Overview!$A$2:$B$19,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="I5" s="3">
+        <v>100</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" s="3">
+        <f>VLOOKUP(G6,Overview!$A$2:$B$19,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="I6" s="3">
+        <v>100</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H7" s="3">
+        <f>VLOOKUP(G7,Overview!$A$2:$B$19,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="I7" s="3">
+        <v>100</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" s="3">
+        <f>VLOOKUP(G8,Overview!$A$2:$B$19,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="I8" s="3">
+        <v>100</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H9" s="3">
+        <f>VLOOKUP(G9,Overview!$A$2:$B$19,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="I9" s="3">
+        <v>100</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H10" s="3">
+        <f>VLOOKUP(G10,Overview!$A$2:$B$19,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="I10" s="3">
+        <v>100</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H11" s="3">
+        <f>VLOOKUP(G11,Overview!$A$2:$B$19,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="I11" s="3">
+        <v>100</v>
+      </c>
+      <c r="J11" s="7"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
+</worksheet>
 </file>
--- a/ExcelToJSONConverter/excel/guideQuest.xlsx
+++ b/ExcelToJSONConverter/excel/guideQuest.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A1E5157-9B7E-414E-9A75-BAA18A66B155}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0229C607-AFEC-4770-87B9-D8DFFA84FB07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -206,10 +206,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>open_guide_key</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>TOURNAMENT</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -247,6 +243,9 @@
   <si>
     <t>gold</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>open_guide_quest</t>
   </si>
 </sst>
 </file>
@@ -706,7 +705,7 @@
         <v>12</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" t="s">
         <v>38</v>
@@ -721,7 +720,7 @@
       </c>
       <c r="B3">
         <f t="shared" ref="B3:B18" si="0">B2+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" t="s">
         <v>39</v>
@@ -737,7 +736,7 @@
       </c>
       <c r="B4">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" t="s">
         <v>40</v>
@@ -753,7 +752,7 @@
       </c>
       <c r="B5">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5" t="s">
         <v>41</v>
@@ -769,7 +768,7 @@
       </c>
       <c r="B6">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" t="s">
         <v>42</v>
@@ -785,7 +784,7 @@
       </c>
       <c r="B7">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" t="s">
         <v>43</v>
@@ -801,7 +800,7 @@
       </c>
       <c r="B8">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D8" t="s">
         <v>44</v>
@@ -817,7 +816,7 @@
       </c>
       <c r="B9">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D9" t="s">
         <v>45</v>
@@ -833,7 +832,7 @@
       </c>
       <c r="B10">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" t="s">
         <v>46</v>
@@ -849,7 +848,7 @@
       </c>
       <c r="B11">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -858,7 +857,7 @@
       </c>
       <c r="B12">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -867,7 +866,7 @@
       </c>
       <c r="B13">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -876,7 +875,7 @@
       </c>
       <c r="B14">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -885,7 +884,7 @@
       </c>
       <c r="B15">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -894,7 +893,7 @@
       </c>
       <c r="B16">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
@@ -903,7 +902,7 @@
       </c>
       <c r="B17">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
@@ -912,7 +911,7 @@
       </c>
       <c r="B18">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
@@ -921,7 +920,7 @@
       </c>
       <c r="B19">
         <f>B18+1</f>
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -1014,7 +1013,7 @@
       </c>
       <c r="G3" s="3">
         <f>VLOOKUP(F3,Overview!$A$2:$B$19,2,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3" s="7">
         <v>100</v>
@@ -1023,7 +1022,7 @@
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="7"/>
       <c r="B4" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="7">
@@ -1031,11 +1030,11 @@
       </c>
       <c r="E4" s="7"/>
       <c r="F4" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G4" s="3">
         <f>VLOOKUP(F4,Overview!$A$2:$B$19,2,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" s="7">
         <v>100</v>
@@ -1044,7 +1043,7 @@
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="7"/>
       <c r="B5" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C5" s="8"/>
       <c r="D5" s="7"/>
@@ -1054,7 +1053,7 @@
       </c>
       <c r="G5" s="3">
         <f>VLOOKUP(F5,Overview!$A$2:$B$19,2,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5" s="7">
         <v>100</v>
@@ -1063,7 +1062,7 @@
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="7"/>
       <c r="B6" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C6" s="8"/>
       <c r="D6" s="7">
@@ -1071,11 +1070,11 @@
       </c>
       <c r="E6" s="7"/>
       <c r="F6" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G6" s="3">
         <f>VLOOKUP(F6,Overview!$A$2:$B$19,2,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" s="7">
         <v>100</v>
@@ -1084,7 +1083,7 @@
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="7"/>
       <c r="B7" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>49</v>
@@ -1098,7 +1097,7 @@
       </c>
       <c r="G7" s="3">
         <f>VLOOKUP(F7,Overview!$A$2:$B$19,2,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7" s="7">
         <v>100</v>
@@ -1107,7 +1106,7 @@
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="7"/>
       <c r="B8" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C8" s="8"/>
       <c r="D8" s="7"/>
@@ -1115,11 +1114,11 @@
         <v>52</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G8" s="3">
         <f>VLOOKUP(F8,Overview!$A$2:$B$19,2,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" s="7">
         <v>100</v>
@@ -1182,7 +1181,7 @@
         <v>9</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -1233,7 +1232,7 @@
       </c>
       <c r="H3" s="3">
         <f>VLOOKUP(G3,Overview!$A$2:$B$19,2,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3" s="3">
         <v>100</v>
@@ -1256,13 +1255,13 @@
       </c>
       <c r="H4" s="3">
         <f>VLOOKUP(G4,Overview!$A$2:$B$19,2,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I4" s="3">
         <v>100</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
@@ -1281,13 +1280,13 @@
       </c>
       <c r="H5" s="3">
         <f>VLOOKUP(G5,Overview!$A$2:$B$19,2,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5" s="3">
         <v>100</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
@@ -1306,13 +1305,13 @@
       </c>
       <c r="H6" s="3">
         <f>VLOOKUP(G6,Overview!$A$2:$B$19,2,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6" s="3">
         <v>100</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
@@ -1331,13 +1330,13 @@
       </c>
       <c r="H7" s="3">
         <f>VLOOKUP(G7,Overview!$A$2:$B$19,2,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I7" s="3">
         <v>100</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
@@ -1356,13 +1355,13 @@
       </c>
       <c r="H8" s="3">
         <f>VLOOKUP(G8,Overview!$A$2:$B$19,2,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I8" s="3">
         <v>100</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
@@ -1381,13 +1380,13 @@
       </c>
       <c r="H9" s="3">
         <f>VLOOKUP(G9,Overview!$A$2:$B$19,2,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I9" s="3">
         <v>100</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
@@ -1406,13 +1405,13 @@
       </c>
       <c r="H10" s="3">
         <f>VLOOKUP(G10,Overview!$A$2:$B$19,2,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I10" s="3">
         <v>100</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
@@ -1429,7 +1428,7 @@
       </c>
       <c r="H11" s="3">
         <f>VLOOKUP(G11,Overview!$A$2:$B$19,2,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I11" s="3">
         <v>100</v>

--- a/ExcelToJSONConverter/excel/guideQuest.xlsx
+++ b/ExcelToJSONConverter/excel/guideQuest.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0229C607-AFEC-4770-87B9-D8DFFA84FB07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6C041E6-6C17-4601-BD5A-C0E549F4BB25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="65">
   <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -222,10 +222,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>DAILY_DUNGEON</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>NORMAL_ATTACK</t>
   </si>
   <si>
@@ -246,6 +242,10 @@
   </si>
   <si>
     <t>open_guide_quest</t>
+  </si>
+  <si>
+    <t>1-3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -327,7 +327,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -353,6 +353,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -932,11 +935,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.75" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.5" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.75" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.125" style="2" bestFit="1" customWidth="1"/>
@@ -1022,7 +1025,7 @@
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="7"/>
       <c r="B4" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="7">
@@ -1030,7 +1033,7 @@
       </c>
       <c r="E4" s="7"/>
       <c r="F4" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G4" s="3">
         <f>VLOOKUP(F4,Overview!$A$2:$B$19,2,FALSE)</f>
@@ -1043,7 +1046,7 @@
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="7"/>
       <c r="B5" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C5" s="8"/>
       <c r="D5" s="7"/>
@@ -1062,7 +1065,7 @@
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="7"/>
       <c r="B6" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C6" s="8"/>
       <c r="D6" s="7">
@@ -1070,7 +1073,7 @@
       </c>
       <c r="E6" s="7"/>
       <c r="F6" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G6" s="3">
         <f>VLOOKUP(F6,Overview!$A$2:$B$19,2,FALSE)</f>
@@ -1083,7 +1086,7 @@
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="7"/>
       <c r="B7" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>49</v>
@@ -1106,7 +1109,7 @@
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="7"/>
       <c r="B8" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C8" s="8"/>
       <c r="D8" s="7"/>
@@ -1114,13 +1117,38 @@
         <v>52</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G8" s="3">
         <f>VLOOKUP(F8,Overview!$A$2:$B$19,2,FALSE)</f>
         <v>1</v>
       </c>
       <c r="H8" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="7"/>
+      <c r="B9" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D9" s="7">
+        <v>2</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" s="3">
+        <f>VLOOKUP(F9,Overview!$A$2:$B$19,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="H9" s="7">
         <v>100</v>
       </c>
     </row>
@@ -1181,7 +1209,7 @@
         <v>9</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -1411,7 +1439,7 @@
         <v>100</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">

--- a/ExcelToJSONConverter/excel/guideQuest.xlsx
+++ b/ExcelToJSONConverter/excel/guideQuest.xlsx
@@ -3,14 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6C041E6-6C17-4601-BD5A-C0E549F4BB25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9B6993C-C1A2-43E2-BB96-B16B3D4002BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
-    <sheet name="GuideQuest" sheetId="3" r:id="rId2"/>
-    <sheet name="GuideQuest_Repeat" sheetId="5" r:id="rId3"/>
+    <sheet name="s_guide_quest" sheetId="3" r:id="rId2"/>
+    <sheet name="s_guide_quest_repeat" sheetId="5" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="66">
   <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -46,10 +46,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>MOVE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>start_stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -128,34 +124,9 @@
     <t>rare_gatcha_ticket</t>
   </si>
   <si>
-    <t>ENEMY_KILL</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TOURNAMENT_PLAY</t>
-  </si>
-  <si>
-    <t>RAID_PLAY</t>
-  </si>
-  <si>
-    <t>GACHA_PROGRESS</t>
-  </si>
-  <si>
-    <t>FARM_RICE_EARN</t>
-  </si>
-  <si>
-    <t>MARKET_GOLD_EARN</t>
-  </si>
-  <si>
-    <t>OFFICE_MISSION_PROGRESS</t>
-  </si>
-  <si>
     <t>DAILY_DUNGEON_PLAY</t>
   </si>
   <si>
-    <t>STAGE_BOSS_KILL</t>
-  </si>
-  <si>
     <t>character</t>
   </si>
   <si>
@@ -222,21 +193,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>NORMAL_ATTACK</t>
-  </si>
-  <si>
-    <t>MAIN_SKILL_USE</t>
-  </si>
-  <si>
-    <t>DASH_USE</t>
-  </si>
-  <si>
-    <t>STORYMODE_PLAY</t>
-  </si>
-  <si>
-    <t>CHARACTER_DEPLOY</t>
-  </si>
-  <si>
     <t>gold</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -246,6 +202,52 @@
   <si>
     <t>1-3</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>enemy_kill</t>
+  </si>
+  <si>
+    <t>tournament_play</t>
+  </si>
+  <si>
+    <t>raid_play</t>
+  </si>
+  <si>
+    <t>gacha_progress</t>
+  </si>
+  <si>
+    <t>farm_rice_earn</t>
+  </si>
+  <si>
+    <t>market_gold_earn</t>
+  </si>
+  <si>
+    <t>office_mission_progress</t>
+  </si>
+  <si>
+    <t>daily_dungeon_play</t>
+  </si>
+  <si>
+    <t>stage_boss_kill</t>
+  </si>
+  <si>
+    <t>move</t>
+  </si>
+  <si>
+    <t>normal_attack</t>
+  </si>
+  <si>
+    <t>main_skill_use</t>
+  </si>
+  <si>
+    <t>dash_use</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>storymode_play</t>
+  </si>
+  <si>
+    <t>character_deploy</t>
   </si>
 </sst>
 </file>
@@ -705,13 +707,13 @@
   <sheetData>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -719,14 +721,14 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3">
         <f t="shared" ref="B3:B18" si="0">B2+1</f>
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="E3">
         <f t="shared" ref="E3:E9" si="1">E2+1</f>
@@ -735,14 +737,14 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B4">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="E4">
         <f t="shared" si="1"/>
@@ -751,14 +753,14 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E5">
         <f t="shared" si="1"/>
@@ -767,14 +769,14 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B6">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="E6">
         <f t="shared" si="1"/>
@@ -783,14 +785,14 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="E7">
         <f t="shared" si="1"/>
@@ -799,14 +801,14 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="E8">
         <f t="shared" si="1"/>
@@ -815,14 +817,14 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="E9">
         <f t="shared" si="1"/>
@@ -831,14 +833,14 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="E10">
         <f t="shared" ref="E10" si="2">E9+1</f>
@@ -847,7 +849,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B11">
         <f t="shared" si="0"/>
@@ -856,7 +858,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B12">
         <f t="shared" si="0"/>
@@ -865,7 +867,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B13">
         <f t="shared" si="0"/>
@@ -874,7 +876,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B14">
         <f t="shared" si="0"/>
@@ -883,7 +885,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B15">
         <f t="shared" si="0"/>
@@ -892,7 +894,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B16">
         <f t="shared" si="0"/>
@@ -901,7 +903,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B17">
         <f t="shared" si="0"/>
@@ -910,7 +912,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B18">
         <f t="shared" si="0"/>
@@ -919,7 +921,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B19">
         <f>B18+1</f>
@@ -957,22 +959,22 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -1004,15 +1006,15 @@
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="7"/>
       <c r="B3" s="7" t="s">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
       <c r="F3" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G3" s="3">
         <f>VLOOKUP(F3,Overview!$A$2:$B$19,2,FALSE)</f>
@@ -1025,7 +1027,7 @@
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="7"/>
       <c r="B4" s="7" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="7">
@@ -1033,7 +1035,7 @@
       </c>
       <c r="E4" s="7"/>
       <c r="F4" s="4" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="G4" s="3">
         <f>VLOOKUP(F4,Overview!$A$2:$B$19,2,FALSE)</f>
@@ -1046,13 +1048,13 @@
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="7"/>
       <c r="B5" s="7" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C5" s="8"/>
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
       <c r="F5" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G5" s="3">
         <f>VLOOKUP(F5,Overview!$A$2:$B$19,2,FALSE)</f>
@@ -1065,7 +1067,7 @@
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="7"/>
       <c r="B6" s="7" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C6" s="8"/>
       <c r="D6" s="7">
@@ -1073,7 +1075,7 @@
       </c>
       <c r="E6" s="7"/>
       <c r="F6" s="4" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="G6" s="3">
         <f>VLOOKUP(F6,Overview!$A$2:$B$19,2,FALSE)</f>
@@ -1086,17 +1088,17 @@
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="7"/>
       <c r="B7" s="7" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="D7" s="7"/>
       <c r="E7" s="7" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G7" s="3">
         <f>VLOOKUP(F7,Overview!$A$2:$B$19,2,FALSE)</f>
@@ -1109,15 +1111,15 @@
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="7"/>
       <c r="B8" s="7" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C8" s="8"/>
       <c r="D8" s="7"/>
       <c r="E8" s="7" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="G8" s="3">
         <f>VLOOKUP(F8,Overview!$A$2:$B$19,2,FALSE)</f>
@@ -1130,19 +1132,19 @@
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="7"/>
       <c r="B9" s="7" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="D9" s="7">
         <v>2</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G9" s="3">
         <f>VLOOKUP(F9,Overview!$A$2:$B$19,2,FALSE)</f>
@@ -1188,28 +1190,28 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="J1" s="1" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -1247,7 +1249,7 @@
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="3"/>
       <c r="B3" s="3" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3">
@@ -1256,7 +1258,7 @@
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H3" s="3">
         <f>VLOOKUP(G3,Overview!$A$2:$B$19,2,FALSE)</f>
@@ -1270,16 +1272,16 @@
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
       <c r="B4" s="3" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="4" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H4" s="3">
         <f>VLOOKUP(G4,Overview!$A$2:$B$19,2,FALSE)</f>
@@ -1289,22 +1291,22 @@
         <v>100</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="3"/>
       <c r="B5" s="3" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="4" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H5" s="3">
         <f>VLOOKUP(G5,Overview!$A$2:$B$19,2,FALSE)</f>
@@ -1314,22 +1316,22 @@
         <v>100</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="3"/>
       <c r="B6" s="3" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H6" s="3">
         <f>VLOOKUP(G6,Overview!$A$2:$B$19,2,FALSE)</f>
@@ -1339,22 +1341,22 @@
         <v>100</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="3"/>
       <c r="B7" s="3" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
       <c r="F7" s="4" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H7" s="3">
         <f>VLOOKUP(G7,Overview!$A$2:$B$19,2,FALSE)</f>
@@ -1364,22 +1366,22 @@
         <v>100</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
       <c r="B8" s="3" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="4" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H8" s="3">
         <f>VLOOKUP(G8,Overview!$A$2:$B$19,2,FALSE)</f>
@@ -1389,22 +1391,22 @@
         <v>100</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="4" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H9" s="3">
         <f>VLOOKUP(G9,Overview!$A$2:$B$19,2,FALSE)</f>
@@ -1414,22 +1416,22 @@
         <v>100</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="3"/>
       <c r="B10" s="3" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
       <c r="F10" s="4" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H10" s="3">
         <f>VLOOKUP(G10,Overview!$A$2:$B$19,2,FALSE)</f>
@@ -1439,20 +1441,20 @@
         <v>100</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="3"/>
       <c r="B11" s="3" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H11" s="3">
         <f>VLOOKUP(G11,Overview!$A$2:$B$19,2,FALSE)</f>
